--- a/data/pack/uk/leche.xlsx
+++ b/data/pack/uk/leche.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K679"/>
+  <dimension ref="A1:K680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37696,7 +37696,7 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>34.44</v>
+        <v>34.21</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>35.82</v>
+        <v>35.61</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -37779,6 +37779,61 @@
         </is>
       </c>
       <c r="K679" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>leche</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Leche</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>100kg</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>UK Defra (gov.uk agricultural statistics)</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
         </is>
@@ -37882,7 +37937,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37948,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9">
@@ -37988,7 +38043,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
